--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487674_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487674_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.723100000000001</v>
+        <v>8.8955</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5219</v>
+        <v>6.0214</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2012</v>
+        <v>2.8741</v>
       </c>
       <c r="G2" t="n">
         <v>8.5029</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0292</v>
+        <v>0.2016</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4262</v>
+        <v>-0.0743</v>
       </c>
       <c r="U2" t="n">
-        <v>0.603</v>
+        <v>0.276</v>
       </c>
       <c r="V2" t="n">
         <v>2.3254</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8571</v>
+        <v>7.3303</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7626</v>
+        <v>5.2631</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0945</v>
+        <v>2.0673</v>
       </c>
       <c r="G3" t="n">
         <v>4.4896</v>
@@ -688,13 +688,13 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4802</v>
+        <v>-0.007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6057</v>
+        <v>-0.1052</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1254</v>
+        <v>0.0982</v>
       </c>
       <c r="V3" t="n">
         <v>1.1015</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7622</v>
+        <v>5.3167</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3656</v>
+        <v>4.1654</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3966</v>
+        <v>1.1513</v>
       </c>
       <c r="G4" t="n">
         <v>3.95</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3928</v>
+        <v>-0.0527</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2434</v>
+        <v>0.0432</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1494</v>
+        <v>-0.0959</v>
       </c>
       <c r="V4" t="n">
         <v>2.7776</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0627</v>
+        <v>3.105</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0205</v>
+        <v>2.981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0422</v>
+        <v>0.124</v>
       </c>
       <c r="G5" t="n">
         <v>1.599</v>
@@ -844,13 +844,13 @@
         <v>3.1045</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9527</v>
+        <v>-0.9104</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1806</v>
+        <v>-0.2201</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7721</v>
+        <v>-0.6903</v>
       </c>
       <c r="V5" t="n">
         <v>0.2821</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3713</v>
+        <v>2.1345</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5736</v>
+        <v>2.1732</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2023</v>
+        <v>-0.0388</v>
       </c>
       <c r="G6" t="n">
         <v>3.7881</v>
@@ -922,13 +922,13 @@
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0608</v>
+        <v>-0.1761</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1828</v>
+        <v>-0.2176</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.122</v>
+        <v>0.0415</v>
       </c>
       <c r="V6" t="n">
         <v>-2.4477</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1364</v>
+        <v>1.1637</v>
       </c>
       <c r="E7" t="n">
         <v>1.0086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1278</v>
+        <v>0.155</v>
       </c>
       <c r="G7" t="n">
         <v>1.1306</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5967</v>
+        <v>0.7668</v>
       </c>
       <c r="E8" t="n">
-        <v>1.467</v>
+        <v>1.8279</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8703</v>
+        <v>-1.0611</v>
       </c>
       <c r="G8" t="n">
         <v>1.5015</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.7467</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6662</v>
+        <v>-0.3054</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2505</v>
+        <v>-0.4413</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3463</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0572</v>
+        <v>0.713</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1636</v>
+        <v>-1.5024</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1064</v>
+        <v>2.2154</v>
       </c>
       <c r="G9" t="n">
         <v>1.347</v>
@@ -1156,13 +1156,13 @@
         <v>2.3284</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8862</v>
+        <v>-0.1161</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6662</v>
+        <v>-0.0051</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.22</v>
+        <v>-0.111</v>
       </c>
       <c r="V9" t="n">
         <v>0.0641</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1995</v>
+        <v>-0.3908</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0187</v>
+        <v>0.7184</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2182</v>
+        <v>-1.1092</v>
       </c>
       <c r="G10" t="n">
         <v>0.8677</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.279</v>
+        <v>0.0878</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6068</v>
+        <v>0.3065</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3277</v>
+        <v>-0.2187</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3463</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3953</v>
+        <v>-1.3348</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4939</v>
+        <v>-1.4333</v>
       </c>
       <c r="F12" t="n">
         <v>0.0985</v>
@@ -1390,10 +1390,10 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9948</v>
+        <v>-0.9343</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3634</v>
+        <v>-0.3028</v>
       </c>
       <c r="U12" t="n">
         <v>-0.6314</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0298</v>
+        <v>-4.5693</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9307</v>
+        <v>-3.77</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0991</v>
+        <v>-0.7993</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2421</v>
@@ -1468,13 +1468,13 @@
         <v>1.5523</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9951</v>
+        <v>-1.5346</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7268</v>
+        <v>-0.5661</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2683</v>
+        <v>-0.9685</v>
       </c>
       <c r="V13" t="n">
         <v>1.506</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.4364</v>
+        <v>22.7393</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1709</v>
+        <v>17.4739</v>
       </c>
       <c r="F14" t="n">
-        <v>5.265400000000001</v>
+        <v>5.2653</v>
       </c>
       <c r="G14" t="n">
         <v>24.4998</v>
@@ -1546,10 +1546,10 @@
         <v>18.433</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.9797</v>
+        <v>-4.677</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7497</v>
+        <v>-1.4469</v>
       </c>
       <c r="U14" t="n">
         <v>-3.2299</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4644</v>
+        <v>2.2637</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6547</v>
+        <v>2.7538</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1903</v>
+        <v>-0.4901</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7996</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5177</v>
+        <v>1.317</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7126</v>
+        <v>0.8117</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8051</v>
+        <v>0.5053</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.334</v>
+        <v>1.9619</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6582</v>
+        <v>2.2588</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3241</v>
+        <v>-0.2969</v>
       </c>
       <c r="G16" t="n">
         <v>0.1261</v>
@@ -1702,13 +1702,13 @@
         <v>2.5224</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1034</v>
+        <v>0.7313</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0471</v>
+        <v>0.5535</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1505</v>
+        <v>0.1778</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2239</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2497</v>
+        <v>-0.3488</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5284</v>
+        <v>2.4293</v>
       </c>
       <c r="F17" t="n">
         <v>-2.7782</v>
@@ -1780,10 +1780,10 @@
         <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1395</v>
+        <v>-0.2386</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.775</v>
+        <v>0.1259</v>
       </c>
       <c r="U17" t="n">
         <v>-0.3645</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6575</v>
+        <v>-1.6208</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4447</v>
+        <v>1.6449</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1022</v>
+        <v>-3.2658</v>
       </c>
       <c r="G18" t="n">
         <v>-3.186</v>
@@ -1858,13 +1858,13 @@
         <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2178</v>
+        <v>-0.1811</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4834</v>
+        <v>-0.2832</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2656</v>
+        <v>0.1021</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2254</v>
+        <v>-3.5959</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7371</v>
+        <v>-1.1587</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4883</v>
+        <v>-2.4372</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.4338</v>
+        <v>-1.1237</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.5626</v>
+        <v>0.7209</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.8712</v>
+        <v>-1.8446</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.73</v>
+        <v>-0.2107</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4994</v>
+        <v>1.0834</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2306</v>
+        <v>-1.2941</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.7038</v>
+        <v>-0.9131</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.0632</v>
+        <v>-0.3625</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6406</v>
+        <v>-0.5506</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7463</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3582</v>
+        <v>-1.1642</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1045</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7442</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3512</v>
+        <v>0.2162</v>
       </c>
       <c r="U19" t="n">
-        <v>0.393</v>
+        <v>0.4296</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2821</v>
+        <v>-2.7298</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2821</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8738</v>
+        <v>-3.802</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2417</v>
+        <v>-0.6592</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1155</v>
+        <v>-3.1428</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8046</v>
@@ -2014,13 +2014,13 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5711</v>
+        <v>0.6429</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5175</v>
+        <v>0.6166</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0536</v>
+        <v>0.0264</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1331</v>
+        <v>-4.1367</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8594</v>
+        <v>-2.8392</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2737</v>
+        <v>-1.2975</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1237</v>
+        <v>-7.4338</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7209</v>
+        <v>-4.5626</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8446</v>
+        <v>-2.8712</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2107</v>
+        <v>-2.73</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0834</v>
+        <v>-1.4994</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2941</v>
+        <v>-1.2306</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9131</v>
+        <v>-4.7038</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3625</v>
+        <v>-3.0632</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5506</v>
+        <v>-1.6406</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1642</v>
+        <v>-1.3582</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>3.1045</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1086</v>
+        <v>1.8329</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4845</v>
+        <v>1.2491</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5931</v>
+        <v>0.5838</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.7298</v>
+        <v>-0.2821</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7298</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.0554</v>
+        <v>-6.0911</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1101</v>
+        <v>-3.3093</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9453</v>
+        <v>-2.7818</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0941</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.321</v>
+        <v>-0.3567</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0296</v>
+        <v>-0.2288</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2914</v>
+        <v>-0.1278</v>
       </c>
       <c r="V22" t="n">
         <v>0.9418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.039999999999999</v>
+        <v>-7.0668</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.0866</v>
+        <v>-6.3859</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9535</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-1.656</v>
@@ -2248,13 +2248,13 @@
         <v>2.7164</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.387</v>
+        <v>0.5863</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5317</v>
+        <v>0.169</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1447</v>
+        <v>0.4172</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5642</v>
@@ -2287,7 +2287,7 @@
         <v>-5.2655</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.1711</v>
+        <v>-17.1712</v>
       </c>
       <c r="G24" t="n">
         <v>-24.4998</v>
@@ -2296,7 +2296,7 @@
         <v>-16.4362</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.063499999999999</v>
+        <v>-8.063500000000001</v>
       </c>
       <c r="J24" t="n">
         <v>4.1959</v>
@@ -2326,13 +2326,13 @@
         <v>18.433</v>
       </c>
       <c r="S24" t="n">
-        <v>4.979700000000001</v>
+        <v>4.979699999999999</v>
       </c>
       <c r="T24" t="n">
         <v>3.23</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7497</v>
+        <v>1.7499</v>
       </c>
       <c r="V24" t="n">
         <v>-2.9164</v>
